--- a/xlsx/tests/calc_tests/named_ranges.xlsx
+++ b/xlsx/tests/calc_tests/named_ranges.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dg-ac/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nhatcher/IronCalc/IronCalc/xlsx/tests/calc_tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD923B89-50D9-1F41-84EE-50A57EE13461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859EBC40-5C93-1E49-BE36-8F5E19DBCD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11780" yWindow="-28300" windowWidth="51200" windowHeight="28300" xr2:uid="{77C5B8DF-38AB-9940-9A87-3D84E35BA886}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="33600" windowHeight="20380" activeTab="4" xr2:uid="{77C5B8DF-38AB-9940-9A87-3D84E35BA886}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,6 @@
     <definedName name="ConstVAT" comment="Constant (number)">0.2</definedName>
     <definedName name="DiscountRate" comment="Single cell">Inputs!$B$3</definedName>
     <definedName name="DoubleTarget" comment="Formula">Inputs!$B$6*2</definedName>
-    <definedName name="DynRevenue" comment="Dynamic (INDEX)">Data!$E$2:INDEX(Data!$E:$E,COUNTA(Data!$A:$A))</definedName>
     <definedName name="DynUnits" comment="Dynamic (OFFSET)">OFFSET(Data!$C$2,0,0,COUNTA(Data!$C:$C)-1,1)</definedName>
     <definedName name="EmptyRange" comment="Empty range">Data!$G$2:$G$5</definedName>
     <definedName name="FirstFiveUnits" comment="Partial range">Data!$C$2:$C$6</definedName>
@@ -67,11 +66,10 @@
     <definedName name="Threshold" comment="Single cell">Inputs!$B$8</definedName>
     <definedName name="TopLeftBlock" comment="2D partial range">Data!$C$2:$D$4</definedName>
     <definedName name="TotalRevenue" comment="Formula">SUM(Data!$E$2:$E$21)</definedName>
-    <definedName name="UnionRange" comment="Union (multi-area)">Data!$C$2:$C$4,Data!$C$19:$C$21</definedName>
     <definedName name="Units" comment="Column range">Data!$C$2:$C$21</definedName>
     <definedName name="UnitsColumn" comment="Whole column">Data!$C:$C</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -117,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="237">
   <si>
     <t>Parameter</t>
   </si>
@@ -539,12 +537,6 @@
     <t>=SUM(DynUnits)</t>
   </si>
   <si>
-    <t>DynRevenue</t>
-  </si>
-  <si>
-    <t>=SUM(DynRevenue)</t>
-  </si>
-  <si>
     <t>Name syntax</t>
   </si>
   <si>
@@ -581,15 +573,6 @@
     <t>=SUM(This_Is_A_Very_Long_Named_Range_For_Testing)</t>
   </si>
   <si>
-    <t>Union range</t>
-  </si>
-  <si>
-    <t>UnionRange</t>
-  </si>
-  <si>
-    <t>=SUM(UnionRange)</t>
-  </si>
-  <si>
     <t>Scope: workbook</t>
   </si>
   <si>
@@ -707,12 +690,6 @@
     <t>=Inputs!$B$6*2</t>
   </si>
   <si>
-    <t>=Data!$E$2:INDEX(Data!$E:$E,COUNTA(Data!$A:$A))</t>
-  </si>
-  <si>
-    <t>Dynamic (INDEX)</t>
-  </si>
-  <si>
     <t>=OFFSET(Data!$C$2,0,0,COUNTA(Data!$C:$C)-1,1)</t>
   </si>
   <si>
@@ -828,12 +805,6 @@
   </si>
   <si>
     <t>=SUM(Data!$E$2:$E$21)</t>
-  </si>
-  <si>
-    <t>=Data!$C$2:$C$4,Data!$C$19:$C$21</t>
-  </si>
-  <si>
-    <t>Union (multi-area)</t>
   </si>
   <si>
     <t>=Data!$C:$C</t>
@@ -1322,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{437B6B5C-1A14-C342-B261-30D17D136990}">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1343,8 +1314,8 @@
         <v>33</v>
       </c>
       <c r="B2" s="4" t="str">
-        <f ca="1">COUNTIF(G5:G63,"PASS")&amp;" / "&amp;ROWS(G5:G63)</f>
-        <v>59 / 59</v>
+        <f ca="1">COUNTIF(G5:G61,"PASS")&amp;" / "&amp;ROWS(G5:G61)</f>
+        <v>57 / 57</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -1423,7 +1394,7 @@
         <v>0.05</v>
       </c>
       <c r="G6" t="str">
-        <f t="shared" ref="G6:G63" si="0">IFERROR(IF(E6=F6,"PASS","FAIL"),"FAIL")</f>
+        <f t="shared" ref="G6:G61" si="0">IFERROR(IF(E6=F6,"PASS","FAIL"),"FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -2599,24 +2570,24 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E52">
-        <f>SUM(DynRevenue)</f>
-        <v>17874</v>
+        <f>SUM(Sales_2024)</f>
+        <v>9269</v>
       </c>
       <c r="F52">
-        <f>SUM(Data!E2:E21)</f>
-        <v>17874</v>
+        <f>SUM(Data!E2:E11)</f>
+        <v>9269</v>
       </c>
       <c r="G52" t="str">
         <f t="shared" si="0"/>
@@ -2625,10 +2596,10 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>143</v>
@@ -2637,12 +2608,12 @@
         <v>144</v>
       </c>
       <c r="E53">
-        <f>SUM(Sales_2024)</f>
-        <v>9269</v>
+        <f>Rate.Commission</f>
+        <v>0.05</v>
       </c>
       <c r="F53">
-        <f>SUM(Data!E2:E11)</f>
-        <v>9269</v>
+        <f>Inputs!E2</f>
+        <v>0.05</v>
       </c>
       <c r="G53" t="str">
         <f t="shared" si="0"/>
@@ -2651,10 +2622,10 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>145</v>
@@ -2663,12 +2634,12 @@
         <v>146</v>
       </c>
       <c r="E54">
-        <f>Rate.Commission</f>
-        <v>0.05</v>
+        <f>_Helper</f>
+        <v>250</v>
       </c>
       <c r="F54">
-        <f>Inputs!E2</f>
-        <v>0.05</v>
+        <f>Inputs!B10</f>
+        <v>250</v>
       </c>
       <c r="G54" t="str">
         <f t="shared" si="0"/>
@@ -2677,129 +2648,129 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E55">
-        <f>_Helper</f>
+        <f>lowercasename</f>
+        <v>50</v>
+      </c>
+      <c r="F55">
+        <f>Inputs!B8</f>
+        <v>50</v>
+      </c>
+      <c r="G55" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>53</v>
+      </c>
+      <c r="B56" t="s">
+        <v>140</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="E56">
+        <f>SUM(This_Is_A_Very_Long_Named_Range_For_Testing)</f>
+        <v>1013</v>
+      </c>
+      <c r="F56">
+        <f>SUM(Data!C2:C21)</f>
+        <v>1013</v>
+      </c>
+      <c r="G56" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>152</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="E57">
+        <f>Scope_Test</f>
+        <v>3</v>
+      </c>
+      <c r="F57">
+        <f>Inputs!B9</f>
+        <v>3</v>
+      </c>
+      <c r="G57" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>155</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E58">
+        <f>Data!Scope_Test</f>
+        <v>12</v>
+      </c>
+      <c r="F58">
+        <f>Data!C2</f>
+        <v>12</v>
+      </c>
+      <c r="G58" t="str">
+        <f t="shared" si="0"/>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>158</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="E59">
+        <f>LocalBonus</f>
         <v>250</v>
       </c>
-      <c r="F55">
+      <c r="F59">
         <f>Inputs!B10</f>
         <v>250</v>
       </c>
-      <c r="G55" t="str">
-        <f t="shared" si="0"/>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56">
-        <v>52</v>
-      </c>
-      <c r="B56" t="s">
-        <v>149</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="E56">
-        <f>lowercasename</f>
-        <v>50</v>
-      </c>
-      <c r="F56">
-        <f>Inputs!B8</f>
-        <v>50</v>
-      </c>
-      <c r="G56" t="str">
-        <f t="shared" si="0"/>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57">
-        <v>53</v>
-      </c>
-      <c r="B57" t="s">
-        <v>142</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="E57">
-        <f>SUM(This_Is_A_Very_Long_Named_Range_For_Testing)</f>
-        <v>1013</v>
-      </c>
-      <c r="F57">
-        <f>SUM(Data!C2:C21)</f>
-        <v>1013</v>
-      </c>
-      <c r="G57" t="str">
-        <f t="shared" si="0"/>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58">
-        <v>54</v>
-      </c>
-      <c r="B58" t="s">
-        <v>154</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="E58">
-        <f>SUM(UnionRange)</f>
-        <v>251</v>
-      </c>
-      <c r="F58">
-        <f>SUM(Data!C2:C4,Data!C19:C21)</f>
-        <v>251</v>
-      </c>
-      <c r="G58" t="str">
-        <f t="shared" si="0"/>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59">
-        <v>55</v>
-      </c>
-      <c r="B59" t="s">
-        <v>157</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="E59">
-        <f>Scope_Test</f>
-        <v>3</v>
-      </c>
-      <c r="F59">
-        <f>Inputs!B9</f>
-        <v>3</v>
-      </c>
       <c r="G59" t="str">
         <f t="shared" si="0"/>
         <v>PASS</v>
@@ -2807,24 +2778,24 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E60">
-        <f>Data!Scope_Test</f>
-        <v>12</v>
+        <f>HiddenName</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F60">
-        <f>Data!C2</f>
-        <v>12</v>
+        <f>Inputs!B4</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G60" t="str">
         <f t="shared" si="0"/>
@@ -2833,89 +2804,35 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E61">
-        <f>LocalBonus</f>
-        <v>250</v>
-      </c>
-      <c r="F61">
-        <f>Inputs!B10</f>
-        <v>250</v>
-      </c>
-      <c r="G61" t="str">
-        <f t="shared" si="0"/>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A62">
-        <v>58</v>
-      </c>
-      <c r="B62" t="s">
-        <v>166</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="E62">
-        <f>HiddenName</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F62">
-        <f>Inputs!B4</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="G62" t="str">
-        <f t="shared" si="0"/>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A63">
-        <v>59</v>
-      </c>
-      <c r="B63" t="s">
-        <v>169</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E63">
         <f>COUNTBLANK(EmptyRange)</f>
         <v>4</v>
       </c>
-      <c r="F63">
+      <c r="F61">
         <f>COUNTBLANK(Data!G2:G5)</f>
         <v>4</v>
       </c>
-      <c r="G63" t="str">
+      <c r="G61" t="str">
         <f t="shared" si="0"/>
         <v>PASS</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G5:G63">
+  <conditionalFormatting sqref="G5:G61">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="PASS">
       <formula>NOT(ISERROR(SEARCH("PASS",G5)))</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G63">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="FAIL">
       <formula>NOT(ISERROR(SEARCH("FAIL",G5)))</formula>
     </cfRule>
@@ -3490,7 +3407,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6D912E-3474-C948-A1AC-F5424B286C3B}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.33203125" customWidth="1"/>
@@ -3501,33 +3418,33 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -3538,10 +3455,10 @@
         <v>128</v>
       </c>
       <c r="B3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D3" t="s">
         <v>38</v>
@@ -3555,10 +3472,10 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D4" t="s">
         <v>42</v>
@@ -3572,13 +3489,13 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" t="s">
         <v>177</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="D5" t="s">
-        <v>182</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -3586,16 +3503,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B6" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D6" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -3603,16 +3520,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B7" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D7" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -3623,10 +3540,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D8" t="s">
         <v>49</v>
@@ -3637,13 +3554,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B9" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D9" t="s">
         <v>122</v>
@@ -3657,13 +3574,13 @@
         <v>118</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D10" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
@@ -3674,13 +3591,13 @@
         <v>120</v>
       </c>
       <c r="B11" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D11" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -3691,10 +3608,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D12" t="s">
         <v>42</v>
@@ -3708,10 +3625,10 @@
         <v>132</v>
       </c>
       <c r="B13" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
@@ -3722,16 +3639,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B14" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D14" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
@@ -3739,16 +3656,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D15" t="s">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
@@ -3756,16 +3673,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>170</v>
+        <v>97</v>
       </c>
       <c r="B16" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D16" t="s">
-        <v>169</v>
+        <v>96</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
@@ -3773,16 +3690,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
@@ -3790,13 +3707,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D18" t="s">
         <v>42</v>
@@ -3807,16 +3724,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>4</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D19" t="s">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
@@ -3824,16 +3741,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="B20" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
@@ -3841,50 +3758,50 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>162</v>
       </c>
       <c r="B21" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>161</v>
       </c>
       <c r="E21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>167</v>
+        <v>99</v>
       </c>
       <c r="B22" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D22" t="s">
-        <v>166</v>
+        <v>96</v>
       </c>
       <c r="E22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>42</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
@@ -3892,16 +3809,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D24" t="s">
-        <v>42</v>
+        <v>202</v>
       </c>
       <c r="E24" t="b">
         <v>1</v>
@@ -3909,16 +3826,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D25" t="s">
-        <v>209</v>
+        <v>42</v>
       </c>
       <c r="E25" t="b">
         <v>1</v>
@@ -3926,16 +3843,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>180</v>
       </c>
       <c r="E26" t="b">
         <v>1</v>
@@ -3943,16 +3860,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="B27" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="D27" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
@@ -3960,16 +3877,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="B28" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D28" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="E28" t="b">
         <v>1</v>
@@ -3977,16 +3894,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B29" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D29" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E29" t="b">
         <v>1</v>
@@ -3994,16 +3911,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D30" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="E30" t="b">
         <v>1</v>
@@ -4011,16 +3928,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="B31" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D31" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E31" t="b">
         <v>1</v>
@@ -4028,16 +3945,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D32" t="s">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="E32" t="b">
         <v>1</v>
@@ -4045,16 +3962,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="D33" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
@@ -4062,16 +3979,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="B34" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="D34" t="s">
-        <v>185</v>
+        <v>38</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
@@ -4079,16 +3996,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B35" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D35" t="s">
-        <v>38</v>
+        <v>217</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
@@ -4096,16 +4013,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="B36" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D36" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E36" t="b">
         <v>1</v>
@@ -4113,16 +4030,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B37" t="s">
+        <v>172</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="D37" t="s">
         <v>177</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="D37" t="s">
-        <v>226</v>
       </c>
       <c r="E37" t="b">
         <v>1</v>
@@ -4130,16 +4047,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D38" t="s">
-        <v>182</v>
+        <v>42</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
@@ -4147,16 +4064,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>222</v>
       </c>
       <c r="B39" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="D39" t="s">
-        <v>42</v>
+        <v>223</v>
       </c>
       <c r="E39" t="b">
         <v>1</v>
@@ -4164,16 +4081,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>229</v>
+        <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="D40" t="s">
-        <v>230</v>
+        <v>46</v>
       </c>
       <c r="E40" t="b">
         <v>1</v>
@@ -4181,16 +4098,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E41" t="b">
         <v>1</v>
@@ -4198,16 +4115,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="B42" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D42" t="s">
-        <v>42</v>
+        <v>227</v>
       </c>
       <c r="E42" t="b">
         <v>1</v>
@@ -4215,16 +4132,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>152</v>
+        <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="D43" t="s">
-        <v>234</v>
+        <v>42</v>
       </c>
       <c r="E43" t="b">
         <v>1</v>
@@ -4232,16 +4149,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="B44" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="D44" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="E44" t="b">
         <v>1</v>
@@ -4249,16 +4166,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="B45" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D45" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="E45" t="b">
         <v>1</v>
@@ -4266,16 +4183,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>126</v>
+        <v>19</v>
       </c>
       <c r="B46" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="D46" t="s">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="E46" t="b">
         <v>1</v>
@@ -4283,16 +4200,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="D47" t="s">
-        <v>238</v>
+        <v>104</v>
       </c>
       <c r="E47" t="b">
         <v>1</v>
@@ -4300,16 +4217,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>19</v>
+        <v>222</v>
       </c>
       <c r="B48" t="s">
-        <v>177</v>
+        <v>231</v>
       </c>
       <c r="C48" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="D48" t="s">
         <v>233</v>
-      </c>
-      <c r="D48" t="s">
-        <v>185</v>
       </c>
       <c r="E48" t="b">
         <v>1</v>
@@ -4317,52 +4234,18 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>105</v>
+        <v>234</v>
       </c>
       <c r="B49" t="s">
-        <v>177</v>
+        <v>235</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>239</v>
+        <v>173</v>
       </c>
       <c r="D49" t="s">
-        <v>104</v>
+        <v>236</v>
       </c>
       <c r="E49" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>229</v>
-      </c>
-      <c r="B50" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="D50" t="s">
-        <v>242</v>
-      </c>
-      <c r="E50" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>243</v>
-      </c>
-      <c r="B51" t="s">
-        <v>244</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="D51" t="s">
-        <v>245</v>
-      </c>
-      <c r="E51" t="b">
         <v>1</v>
       </c>
     </row>
